--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0003T0006Z000C1N40_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0003T0006Z000C1N40_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.74923312161837</v>
+        <v>6.621750382262986</v>
       </c>
       <c r="D2" t="n">
-        <v>65.26616378186151</v>
+        <v>10.6057516145525</v>
       </c>
       <c r="E2" t="n">
-        <v>13.27259267209601</v>
+        <v>2.156796309215602</v>
       </c>
       <c r="F2" t="n">
-        <v>15.54787739263859</v>
+        <v>2.526530076303771</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>8.015609770940699</v>
+        <v>1.302536587777864</v>
       </c>
       <c r="D3" t="n">
-        <v>56.62428875719066</v>
+        <v>9.201446923043482</v>
       </c>
       <c r="E3" t="n">
-        <v>13.27259267209601</v>
+        <v>2.156796309215602</v>
       </c>
       <c r="F3" t="n">
-        <v>15.54787739263859</v>
+        <v>2.526530076303771</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.59984016237419</v>
+        <v>4.484974026385805</v>
       </c>
       <c r="D4" t="n">
-        <v>54.41588372460513</v>
+        <v>8.842581105248334</v>
       </c>
       <c r="E4" t="n">
-        <v>13.27259267209601</v>
+        <v>2.156796309215602</v>
       </c>
       <c r="F4" t="n">
-        <v>15.54787739263859</v>
+        <v>2.526530076303771</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.96351393264352</v>
+        <v>3.894071014054572</v>
       </c>
       <c r="D5" t="n">
-        <v>46.78090354897851</v>
+        <v>7.601896826709008</v>
       </c>
       <c r="E5" t="n">
-        <v>13.27259267209601</v>
+        <v>2.156796309215602</v>
       </c>
       <c r="F5" t="n">
-        <v>15.54787739263859</v>
+        <v>2.526530076303771</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.40075756488817</v>
+        <v>4.290123104294328</v>
       </c>
       <c r="D6" t="n">
-        <v>42.53295555109918</v>
+        <v>6.911605277053616</v>
       </c>
       <c r="E6" t="n">
-        <v>13.27259267209601</v>
+        <v>2.156796309215602</v>
       </c>
       <c r="F6" t="n">
-        <v>15.54787739263859</v>
+        <v>2.526530076303771</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>53.37005421498584</v>
+        <v>8.672633809935199</v>
       </c>
       <c r="D7" t="n">
-        <v>52.42189749040016</v>
+        <v>8.518558342190026</v>
       </c>
       <c r="E7" t="n">
-        <v>13.27259267209601</v>
+        <v>2.156796309215602</v>
       </c>
       <c r="F7" t="n">
-        <v>15.54787739263859</v>
+        <v>2.526530076303771</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>52.49080911852037</v>
+        <v>8.529756481759559</v>
       </c>
       <c r="D8" t="n">
-        <v>51.59092893628245</v>
+        <v>8.383525952145899</v>
       </c>
       <c r="E8" t="n">
-        <v>13.27259267209601</v>
+        <v>2.156796309215602</v>
       </c>
       <c r="F8" t="n">
-        <v>15.54787739263859</v>
+        <v>2.526530076303771</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>54.73762707100231</v>
+        <v>8.894864399037875</v>
       </c>
       <c r="D9" t="n">
-        <v>54.93759928948057</v>
+        <v>8.927359884540593</v>
       </c>
       <c r="E9" t="n">
-        <v>13.27259267209601</v>
+        <v>2.156796309215602</v>
       </c>
       <c r="F9" t="n">
-        <v>15.54787739263859</v>
+        <v>2.526530076303771</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>44.32517269181467</v>
+        <v>7.202840562419884</v>
       </c>
       <c r="D10" t="n">
-        <v>43.68629945571234</v>
+        <v>7.099023661553255</v>
       </c>
       <c r="E10" t="n">
-        <v>13.27259267209601</v>
+        <v>2.156796309215602</v>
       </c>
       <c r="F10" t="n">
-        <v>15.54787739263859</v>
+        <v>2.526530076303771</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>45.68146542703795</v>
+        <v>7.423238131893667</v>
       </c>
       <c r="D11" t="n">
-        <v>45.18954368691862</v>
+        <v>7.343300849124276</v>
       </c>
       <c r="E11" t="n">
-        <v>13.27259267209601</v>
+        <v>2.156796309215602</v>
       </c>
       <c r="F11" t="n">
-        <v>15.54787739263859</v>
+        <v>2.526530076303771</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>41.89168442153817</v>
+        <v>6.807398718499953</v>
       </c>
       <c r="D12" t="n">
-        <v>42.33301907265752</v>
+        <v>6.879115599306847</v>
       </c>
       <c r="E12" t="n">
-        <v>13.27259267209601</v>
+        <v>2.156796309215602</v>
       </c>
       <c r="F12" t="n">
-        <v>15.54787739263859</v>
+        <v>2.526530076303771</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>30.28116589380564</v>
+        <v>4.920689457743417</v>
       </c>
       <c r="D13" t="n">
-        <v>30.02637085122389</v>
+        <v>4.879285263323882</v>
       </c>
       <c r="E13" t="n">
-        <v>13.27259267209601</v>
+        <v>2.156796309215602</v>
       </c>
       <c r="F13" t="n">
-        <v>15.54787739263859</v>
+        <v>2.526530076303771</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>63.00822851713077</v>
+        <v>10.23883713403375</v>
       </c>
       <c r="D14" t="n">
-        <v>40.39481896311653</v>
+        <v>6.564158081506437</v>
       </c>
       <c r="E14" t="n">
-        <v>13.27259267209601</v>
+        <v>2.156796309215602</v>
       </c>
       <c r="F14" t="n">
-        <v>15.54787739263859</v>
+        <v>2.526530076303771</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>46.60114770039759</v>
+        <v>7.572686501314609</v>
       </c>
       <c r="D15" t="n">
-        <v>20.15519782547707</v>
+        <v>3.275219646640024</v>
       </c>
       <c r="E15" t="n">
-        <v>13.27259267209601</v>
+        <v>2.156796309215602</v>
       </c>
       <c r="F15" t="n">
-        <v>15.54787739263859</v>
+        <v>2.526530076303771</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>46.4403392855905</v>
+        <v>7.546555133908457</v>
       </c>
       <c r="D16" t="n">
-        <v>15.95131481867387</v>
+        <v>2.592088658034503</v>
       </c>
       <c r="E16" t="n">
-        <v>13.27259267209601</v>
+        <v>2.156796309215602</v>
       </c>
       <c r="F16" t="n">
-        <v>15.54787739263859</v>
+        <v>2.526530076303771</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>53.11664003719005</v>
+        <v>8.631454006043384</v>
       </c>
       <c r="D17" t="n">
-        <v>53.34926672944658</v>
+        <v>8.669255843535069</v>
       </c>
       <c r="E17" t="n">
-        <v>13.27259267209601</v>
+        <v>2.156796309215602</v>
       </c>
       <c r="F17" t="n">
-        <v>15.54787739263859</v>
+        <v>2.526530076303771</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>52.56398581932775</v>
+        <v>8.54164769564076</v>
       </c>
       <c r="D18" t="n">
-        <v>53.30864990886599</v>
+        <v>8.662655610190724</v>
       </c>
       <c r="E18" t="n">
-        <v>13.27259267209601</v>
+        <v>2.156796309215602</v>
       </c>
       <c r="F18" t="n">
-        <v>15.54787739263859</v>
+        <v>2.526530076303771</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>41.72971250876537</v>
+        <v>6.781078282674374</v>
       </c>
       <c r="D19" t="n">
-        <v>13.44204298254082</v>
+        <v>2.184331984662883</v>
       </c>
       <c r="E19" t="n">
-        <v>13.27259267209601</v>
+        <v>2.156796309215602</v>
       </c>
       <c r="F19" t="n">
-        <v>15.54787739263859</v>
+        <v>2.526530076303771</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>29.68829345269234</v>
+        <v>4.824347686062505</v>
       </c>
       <c r="D20" t="n">
-        <v>11.89684877488764</v>
+        <v>1.933237925919241</v>
       </c>
       <c r="E20" t="n">
-        <v>13.27259267209601</v>
+        <v>2.156796309215602</v>
       </c>
       <c r="F20" t="n">
-        <v>15.54787739263859</v>
+        <v>2.526530076303771</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
